--- a/outputs/evaluation/requirement/design/v1/CF_M05/second/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M05/second/CF_M05_req_eval.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7576000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9231</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="9">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>0.96</v>
+        <v>0.9615</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8276</v>
+        <v>0.8475</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9492</v>
+        <v>0.9479</v>
       </c>
     </row>
     <row r="16">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9167</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="19">
@@ -627,10 +627,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,11 +761,14 @@
           <t>Translations must be complete and correct in all supported languages.</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -781,11 +782,14 @@
           <t>Complete and correct translations in both languages.</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>CF_M05_R12</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -816,6 +820,14 @@
           <t>The system shall display a list of applications to which the authenticated user has access.</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -829,6 +841,10 @@
           <t>View the portal applications to which the user has access.</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -859,6 +875,14 @@
           <t>The system shall allow users to access applications from the portal.</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -872,6 +896,10 @@
           <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -902,6 +930,14 @@
           <t>The system shall allow users to access the portal through personal credential authentication.</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -915,6 +951,10 @@
           <t>Access the portal using credential authentication personal.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -945,6 +985,14 @@
           <t>The system shall prevent users from accessing data belonging to other clients.</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>FR</t>
@@ -958,6 +1006,10 @@
           <t>Ensure that other customers' data cannot be accessed.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -988,6 +1040,14 @@
           <t>The system shall allow administrators to assign or revoke application access for users.</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1001,63 +1061,83 @@
           <t>Give or remove access to applications from users.</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_11</t>
+          <t>R_30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M05_R06</t>
+          <t>CF_M05_R25</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9261</v>
+        <v>0.916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The system shall convert any mention of the old name to the new name.</t>
-        </is>
-      </c>
+          <t>No user shall be able to access data belonging to other clients.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>R_29</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Convert any mention of the old name to the new name.</t>
-        </is>
-      </c>
+          <t>No user can access data from other customers.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CF_M05_R24</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M05_R04</t>
+          <t>CF_M05_R06</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9397</v>
+        <v>0.9261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1071,7 +1151,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The system shall restrict data visualization and actions (create, modify, delete) based on the user's assigned roles.</t>
+          <t>The system shall convert any mention of the old name to the new name.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1080,192 +1168,205 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
+          <t>Convert any mention of the old name to the new name.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>R_07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CF_M05_R04</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9397</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The system shall restrict data visualization and actions (create, modify, delete) based on the user's assigned roles.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>49</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>R_16</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>CF_M05_R11</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>0.9583</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>80% of users shall not need to ask for help from third parties to use the application.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>53</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>80% of users do not need to ask for help from a third party to do
 use the application.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>CF_M05_R10</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>R_29</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CF_M05_R24</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.9611</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>The application must manage a strict separation of data for each client.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>C_09</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>55</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>The application must manage a strict separation of data for each customer.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>CF_M05_C09</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M05_R23</t>
+          <t>CF_M05_R24</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9721</v>
+        <v>0.9611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication and permission verification mechanism to ensure users only access authorized information.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>R_27</t>
-        </is>
-      </c>
+          <t>The application must manage a strict separation of data for each client.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>C_09</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>CF_M05_R22</t>
-        </is>
-      </c>
+          <t>The application must manage a strict separation of data for each customer.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>CF_M05_C09</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R_20</t>
+          <t>R_28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M05_R15</t>
+          <t>CF_M05_R23</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9755</v>
+        <v>0.9721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1274,410 +1375,440 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The learning time for new functionalities should not exceed 5 minutes.</t>
-        </is>
-      </c>
+          <t>The system must have a secure authentication and permission verification mechanism to ensure users only access authorized information.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>R_19</t>
-        </is>
-      </c>
+          <t>R_27</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Learning time for new features should not exceed 5 min.</t>
-        </is>
-      </c>
+          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CF_M05_R14</t>
-        </is>
-      </c>
+          <t>CF_M05_R22</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>R_20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CF_M05_R15</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The learning time for new functionalities should not exceed 5 minutes.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>R_19</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>53</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Learning time for new features should not exceed 5 min.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CF_M05_R14</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>R_27</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>CF_M05_R22</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>0.9762999999999999</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>The system must allow the creation, query, modification, and deletion of data for authorized users.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>C_08</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>54</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>The system must allow the creation, consultation, modification and
 data deletion for authorized users.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>CF_M05_C08</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R_21</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CF_M05_R16</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.9782</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Query operations must have a load time of less than 1 second.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>53</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Query operations should have load time lower than 1 second.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>CF_M05_C05</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>R_21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CF_M05_R16</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Query operations must have a load time of less than 1 second.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>53</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Query operations should have load time lower than 1 second.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>CF_M05_C05</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>R_26</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>CF_M05_R21</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>0.9821</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>System availability must be at least 99.9%, even during peak usage times.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>54</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>System availability must be at least 99.9%, even
 during times of intensive use.</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>CF_M05_R20</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R_24</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CF_M05_R19</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.9821</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>System availability must be at least 99.9%, even during peak usage times.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>R_23</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>54</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>CF_M05_R18</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R_19</t>
+          <t>R_24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M05_R14</t>
+          <t>CF_M05_R19</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9827</v>
+        <v>0.9821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The user must be able to perform new operations without special training.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>C_04</t>
-        </is>
-      </c>
+          <t>System availability must be at least 99.9%, even during peak usage times.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>R_23</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The user must be able to perform the new operations without special training.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>CF_M05_C04</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CF_M05_R18</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R_14</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M05_R09</t>
+          <t>CF_M05_R14</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9832</v>
+        <v>0.9827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Design, colors, fonts, and organization must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>R_13</t>
-        </is>
-      </c>
+          <t>The user must be able to perform new operations without special training.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>C_04</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>CF_M05_R08</t>
-        </is>
-      </c>
+          <t>The user must be able to perform the new operations without special training.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>CF_M05_C04</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>R_14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CF_M05_R09</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Design, colors, fonts, and organization must be consistent with the old version.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>R_13</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CF_M05_R08</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.9885</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>C_01</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1685,258 +1816,265 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>CF_M05_C01</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CF_M05_R08</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>R_13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CF_M05_R08</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9885</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The new content must maintain visual coherence with the design of the old version of the application.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>C_01</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>52</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>CF_M05_C01</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>CF_M05_R20</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>0.9921</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>The web application must support a large number of concurrent users without degrading performance.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>C_07</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>54</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>The web application must support a large number of simultaneous users
 without degrading its performance.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>CF_M05_C07</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>R_22</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CF_M05_R17</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.9937</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Response time must not exceed 1 second in 95% of queries.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R_21</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>53</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Response time should not exceed 1 second in 95% of queries.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>CF_M05_R16</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>R_22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CF_M05_R17</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>criterion</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Response time must not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>R_21</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>53</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Response time should not exceed 1 second in 95% of queries.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CF_M05_R16</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>CF_M05_R18</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C24" t="n">
         <v>0.9953</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>The web application must guarantee continuous and stable operation, ensuring availability at all times.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>C_06</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
         <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>54</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>The web application must guarantee continuous and stable operation,
 ensuring its availability at any time.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>CF_M05_C06</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>R_15</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CF_M05_R10</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>The system must be easy to use for any user.</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>C_02</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>53</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>The system must be easy to use for any user.</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>CF_M05_C02</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R_17</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M05_R12</t>
+          <t>CF_M05_R10</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1954,14 +2092,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>The application must be available in multiple languages.</t>
+          <t>The system must be easy to use for any user.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C_03</t>
-        </is>
-      </c>
+          <t>C_02</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1972,19 +2113,76 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>The system must be easy to use for any user.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>CF_M05_C02</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R_17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CF_M05_R12</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>The application must be available in multiple languages.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>C_03</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>53</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>The application must be available in multiple languages.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>CF_M05_C03</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1997,7 +2195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2185,37 +2383,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_30</t>
+          <t>R_31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>Constraint</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No user shall be able to access data belonging to other clients.</t>
+          <t>Primary keys must be defined for: User, Language, ClusterType, Application, Authority, Role, Brand, and Cluster.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_R05</t>
+          <t>CF_M05_R23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ensure that other customers' data cannot be accessed.</t>
+          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.6833</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_31</t>
+          <t>R_32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2225,27 +2423,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Primary keys must be defined for: User, Language, ClusterType, Application, Authority, Role, Brand, and Cluster.</t>
+          <t>Dates must be valid and cannot be in the future.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M05_R23</t>
+          <t>CF_M05_R19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
+          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.6833</v>
+        <v>0.5909</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_32</t>
+          <t>R_33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2255,51 +2453,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dates must be valid and cannot be in the future.</t>
+          <t>Elements of the same type cannot share the same code.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M05_R19</t>
+          <t>CF_M05_R25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>System availability must be at least 99.9%, even during times of intensive use.</t>
+          <t>No user can access data from other customers.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.5909</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>R_33</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Constraint</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Elements of the same type cannot share the same code.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CF_M05_R24</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>The application must manage a strict separation of data for each customer.</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.6506</v>
+        <v>0.6578000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2313,7 +2481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2351,55 +2519,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_R25</t>
+          <t>CF_M05_R26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The system shall allow users to access the portal through personal credential authentication.</t>
+          <t>The system must be easy to use for any user.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M05_R26</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Functionality for generating graphs and interactive panels that represent communication statistics, traffic volume, response times and incidents, facilitating more intuitive and faster analysis.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>R_15</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>The system must be easy to use for any user.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
         <v>0.6278</v>
       </c>
     </row>
